--- a/order_forms/038_smart_facility_energy_meter_order_form--order_forms.xlsx
+++ b/order_forms/038_smart_facility_energy_meter_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'smart'}</t>
+          <t>smart</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Smart'}</t>
+          <t>Smart</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'standard'}</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Standard'}</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in-house'}</t>
+          <t>in-house</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In-house'}</t>
+          <t>In-house</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'external'}</t>
+          <t>external</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'External'}</t>
+          <t>External</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'On-site'}</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'off-site'}</t>
+          <t>off-site</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Off-site'}</t>
+          <t>Off-site</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'done'}</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Done'}</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
